--- a/data/trans_orig/P37A$otros-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37A$otros-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>683384</t>
+          <t>682414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1377241</t>
+          <t>1377381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>960167</t>
+          <t>961784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1923584</t>
+          <t>1923547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671817</t>
+          <t>672193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677943</t>
+          <t>678911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1354585</t>
+          <t>1355221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1361590</t>
+          <t>1361583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>936920</t>
+          <t>936900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1034166</t>
+          <t>1034217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1973754</t>
+          <t>1972999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1979967</t>
+          <t>1979970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3268128</t>
+          <t>3267704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3275663</t>
+          <t>3275667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3369041</t>
+          <t>3368411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3378211</t>
+          <t>3378213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6640583</t>
+          <t>6640059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6651935</t>
+          <t>6652016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>689687</t>
+          <t>690478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1392476</t>
+          <t>1392844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1012748</t>
+          <t>1013114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1025070</t>
+          <t>1024261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2041215</t>
+          <t>2042726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049171</t>
+          <t>2049169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>751324</t>
+          <t>753128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>770938</t>
+          <t>769999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1527484</t>
+          <t>1527449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3419291</t>
+          <t>3420023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3546425</t>
+          <t>3546471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3556358</t>
+          <t>3556359</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6971069</t>
+          <t>6969288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6982088</t>
+          <t>6981896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665206</t>
+          <t>664267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673777</t>
+          <t>673775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>659178</t>
+          <t>658351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670086</t>
+          <t>670379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1329059</t>
+          <t>1330210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343069</t>
+          <t>1342970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1012483</t>
+          <t>1013327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1032900</t>
+          <t>1034136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1041919</t>
+          <t>1041923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2051288</t>
+          <t>2051620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2062762</t>
+          <t>2062676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,82 +5313,82 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>1050</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8485</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3168</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>751067</t>
+          <t>751012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758502</t>
+          <t>758505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1536082</t>
+          <t>1535085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927859</t>
+          <t>926706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936774</t>
+          <t>936779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1035842</t>
+          <t>1035778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1967022</t>
+          <t>1968125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1979761</t>
+          <t>1979769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36172</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3370420</t>
+          <t>3371101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3387421</t>
+          <t>3387621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3524309</t>
+          <t>3524112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3538608</t>
+          <t>3538579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6902720</t>
+          <t>6902301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6923665</t>
+          <t>6923742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,22 +6639,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>630336</t>
+          <t>685434</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623574</t>
+          <t>677977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>634054</t>
+          <t>689320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>717594</t>
+          <t>725606</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>709489</t>
+          <t>717669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>721436</t>
+          <t>729431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1347932</t>
+          <t>1411039</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1338456</t>
+          <t>1401126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1353715</t>
+          <t>1417459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,69 +6912,69 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14927</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9871</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24388</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14531</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8915</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22747</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>27975</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15908</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -7025,67 +7025,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1180123</t>
+          <t>1035870</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1165677</t>
+          <t>1021397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1187640</t>
+          <t>1042118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1056547</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1047086</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1061603</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>97,72%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1497</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>944120</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>935904</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>949736</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2124244</t>
+          <t>2092416</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2109577</t>
+          <t>2078719</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2135608</t>
+          <t>2100779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29065</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>696999</t>
+          <t>793388</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>689475</t>
+          <t>785356</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701456</t>
+          <t>798369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>924828</t>
+          <t>800736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>914199</t>
+          <t>788476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>930345</t>
+          <t>806193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1621828</t>
+          <t>1594125</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1608981</t>
+          <t>1580680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1629579</t>
+          <t>1601815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,17 +7633,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>922059</t>
+          <t>985199</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916074</t>
+          <t>979002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925159</t>
+          <t>988085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1090907</t>
+          <t>1114903</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1087339</t>
+          <t>1110842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1093360</t>
+          <t>1117298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2012966</t>
+          <t>2100102</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2006464</t>
+          <t>2092594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2017109</t>
+          <t>2104134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>47690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84626</t>
+          <t>91698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3429518</t>
+          <t>3499890</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3415555</t>
+          <t>3485072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3440471</t>
+          <t>3510718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3677450</t>
+          <t>3697792</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3664467</t>
+          <t>3681598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3687953</t>
+          <t>3707876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7106969</t>
+          <t>7197682</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7087471</t>
+          <t>7178018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7122896</t>
+          <t>7213508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
